--- a/outputs/Revenue_Test_Workpaper.xlsx
+++ b/outputs/Revenue_Test_Workpaper.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Population Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Target Testing'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Target Testing'!$A$2:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'MUS Sample'!$A$2:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Population Summary'!$A$1:$E$1</definedName>
   </definedNames>
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,11 +102,17 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -116,9 +122,6 @@
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -493,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -526,146 +529,210 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>500000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Inherent Risk</t>
+          <t>Target Testing</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Disabled</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Control Risk</t>
+          <t>Target Testing Note</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Higher</t>
+          <t>Target testing not performed - MUS applied to full population</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>SAP Level</t>
+          <t>Inherent Risk</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Persuasive</t>
+          <t>Lower</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>90</v>
+          <t>Control Risk</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Higher</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Cutoff Date</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>45473</v>
+          <t>SAP Level</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Persuasive</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Test Negatives</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="b">
-        <v>0</v>
+          <t>Confidence Level</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Run ID</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>08e477fb-aa07-4873-ad28-ccae50a8d580</t>
-        </is>
+          <t>RIA (Risk of Incorrect Acceptance)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Date/Time of run</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>46135.94092807861</v>
+          <t>Confidence Factor (Poisson, 0 expected misstatements)</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Total population count</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>50</v>
+          <t>MUS Sample Size Formula</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>CEILING((Population Value × Confidence Factor) / Tolerable Misstatement)</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Total population value</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>21218088.66</v>
+          <t>MUS Sample Size</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Less Target Tested Value</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>17949446.31</v>
+          <t>Cutoff Date</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>45473</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Residual Population Value used for MUS</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>3268642.35</v>
+          <t>Test Negatives</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Run ID</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>24856f95-4fa1-4ad5-bce2-210aff67637c</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Date/Time of run</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>46139.86147495517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Total population count</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Total population value</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>21218088.66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Less Target Tested Value</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Residual Population Value used for MUS (positive amounts)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>21218088.66</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Target testing threshold</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>250000</v>
-      </c>
+      <c r="B23" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -678,733 +745,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Target testing not performed - MUS applied to full population</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Threshold Used</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Reason Selected</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00043</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
-        <v>45433</v>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Northwind Distribution LLC</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>340461.42</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00044</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>45321</v>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Orchard Financial Services</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>442509.44</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-LARGE-004</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>45421</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Contoso Retail Group</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2523407.5</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-LARGE-002</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>45292</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Pioneer Telecom</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>2532742.65</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00019</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>45309</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Northwind Distribution LLC</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>330970.4</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00007</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>45435</v>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BlueRock Logistics Inc.</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>358293.79</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00023</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>45382</v>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BlueRock Logistics Inc.</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>335417.41</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-LARGE-005</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>45368</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Orchard Financial Services</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1888410.04</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-LARGE-001</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>45367</v>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Summit IT Services</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1276776.07</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00014</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>45446</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Redwood Healthcare Partners</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>403757.01</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00017</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>45452</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Evergreen Construction Ltd.</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>442840.42</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00031</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>45346</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Evergreen Construction Ltd.</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>438307.45</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00029</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>45306</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>BlueRock Logistics Inc.</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>411079.49</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00003</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>45318</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Orchard Financial Services</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>370593.2</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00027</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>45361</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Orchard Financial Services</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>344392.82</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00006</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>45351</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Crescent Energy Solutions</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>301407.35</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00036</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>45441</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Summit IT Services</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>449013.62</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00004</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>45431</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Contoso Retail Group</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>295655.76</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00016</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n">
-        <v>45388</v>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Contoso Retail Group</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>276468.28</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00020</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n">
-        <v>45366</v>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Contoso Retail Group</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>427803.54</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-LARGE-003</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>45359</v>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Crescent Energy Solutions</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>2333433.85</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00032</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>45372</v>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>BlueRock Logistics Inc.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>328063.89</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00024</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>45471</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Orchard Financial Services</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>324369.66</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00010</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>45293</v>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Fabrikam Manufacturing Co.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>349371.56</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>INV-2024-00013</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>45316</v>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Apex Industrial Supply</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>423899.69</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Total value</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>17949446.31</v>
-      </c>
-      <c r="F28" s="3" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1415,23 +810,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>MUS sample drawn from residual population (total less target-tested items).</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>MUS sample drawn from full population (target testing not performed).</t>
         </is>
       </c>
     </row>
@@ -1483,23 +878,23 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00028</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>45348</v>
+          <t>INV-2024-LARGE-004</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>45421</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Orchard Financial Services</t>
+          <t>Contoso Retail Group</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>162817.08</v>
+        <v>2523407.5</v>
       </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -1513,23 +908,23 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00009</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>45406</v>
+          <t>INV-2024-LARGE-002</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>45292</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Evergreen Construction Ltd.</t>
+          <t>Pioneer Telecom</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>139817.16</v>
+        <v>2532742.65</v>
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -1543,23 +938,23 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00030</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>45372</v>
+          <t>INV-2024-00023</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>45382</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Summit IT Services</t>
+          <t>BlueRock Logistics Inc.</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>134602.7</v>
+        <v>335417.41</v>
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -1573,11 +968,11 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00045</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>45360</v>
+          <t>INV-2024-LARGE-005</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>45368</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -1585,11 +980,11 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>170747.56</v>
+        <v>1888410.04</v>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -1603,23 +998,23 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00033</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>45393</v>
+          <t>INV-2024-00014</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>45446</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Orchard Financial Services</t>
+          <t>Redwood Healthcare Partners</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>229967.07</v>
+        <v>403757.01</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -1633,11 +1028,11 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00002</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>45362</v>
+          <t>INV-2024-00029</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>45306</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
@@ -1645,11 +1040,11 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>112382.16</v>
+        <v>411079.49</v>
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -1663,11 +1058,11 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-00035</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>45435</v>
+          <t>INV-2024-00006</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>45351</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -1675,11 +1070,11 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>132108.06</v>
+        <v>301407.35</v>
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n">
-        <v>466948.9071428571</v>
+        <v>1928917.150909091</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -1688,40 +1083,100 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="4" t="n"/>
+      <c r="A10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-LARGE-003</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>45359</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Crescent Energy Solutions</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>2333433.85</v>
+      </c>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="G10" s="4" t="n">
+        <v>1928917.150909091</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Residual population MUS: cumulative value crossed sampling interval point</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-00010</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>45293</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Fabrikam Manufacturing Co.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>349371.56</v>
+      </c>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n">
+        <v>1928917.150909091</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Residual population MUS: cumulative value crossed sampling interval point</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Sample size</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="C13" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Total value</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>1082441.79</v>
-      </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="3" t="n"/>
+      <c r="E13" s="11" t="n">
+        <v>11079026.86</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
@@ -1750,13 +1205,13 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Pre-cutoff transactions (before 30/06/2024)</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
-      <c r="D1" s="12" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="D1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1764,7 +1219,7 @@
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -1774,7 +1229,7 @@
           <t>Customer</t>
         </is>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -1796,7 +1251,7 @@
           <t>INV-2024-00024</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="12" t="n">
         <v>45471</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -1804,7 +1259,7 @@
           <t>Orchard Financial Services</t>
         </is>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="13" t="n">
         <v>324369.66</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -1819,7 +1274,7 @@
           <t>INV-2024-00008</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="12" t="n">
         <v>45471</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -1827,7 +1282,7 @@
           <t>Crescent Energy Solutions</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <v>210340.39</v>
       </c>
       <c r="E4" t="inlineStr">
@@ -1842,7 +1297,7 @@
           <t>INV-2024-00001</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>45455</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -1850,7 +1305,7 @@
           <t>Contoso Retail Group</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="13" t="n">
         <v>13480.37</v>
       </c>
       <c r="E5" t="inlineStr">
@@ -1865,7 +1320,7 @@
           <t>INV-2024-00022</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>45454</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -1873,7 +1328,7 @@
           <t>Apex Industrial Supply</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="13" t="n">
         <v>82164.39</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -1888,7 +1343,7 @@
           <t>INV-2024-00017</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="12" t="n">
         <v>45452</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -1896,7 +1351,7 @@
           <t>Evergreen Construction Ltd.</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>442840.42</v>
       </c>
       <c r="E7" t="inlineStr">
@@ -1906,17 +1361,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="11" t="n"/>
-      <c r="D8" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="D8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Post-cutoff transactions (after 30/06/2024)</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="D9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="D9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1924,7 +1379,7 @@
           <t>Invoice Number</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
@@ -1934,7 +1389,7 @@
           <t>Customer</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -1972,7 +1427,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2008,7 +1463,7 @@
           <t>INV-2024-00040</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="6" t="n">
         <v>45332</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -2031,7 +1486,7 @@
           <t>INV-2024-00028</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
         <v>45348</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2044,7 +1499,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2054,7 +1509,7 @@
           <t>INV-2024-00043</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="6" t="n">
         <v>45433</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2067,7 +1522,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2077,7 +1532,7 @@
           <t>INV-2024-00044</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>45321</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2090,7 +1545,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2100,7 +1555,7 @@
           <t>INV-2024-00042</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>45411</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2123,7 +1578,7 @@
           <t>INV-2024-LARGE-004</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>45421</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2136,7 +1591,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2146,7 +1601,7 @@
           <t>INV-2024-LARGE-002</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>45292</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2159,7 +1614,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2169,7 +1624,7 @@
           <t>INV-2024-00019</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>45309</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2182,7 +1637,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2192,7 +1647,7 @@
           <t>INV-2024-00007</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>45435</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2205,7 +1660,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2215,7 +1670,7 @@
           <t>INV-2024-00023</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>45382</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2228,7 +1683,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2238,7 +1693,7 @@
           <t>INV-2024-00015</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>45409</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2261,7 +1716,7 @@
           <t>INV-2024-00012</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>45378</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -2284,7 +1739,7 @@
           <t>INV-2024-LARGE-005</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>45368</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -2297,7 +1752,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2307,7 +1762,7 @@
           <t>INV-2024-00037</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>45394</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2330,7 +1785,7 @@
           <t>INV-2024-LARGE-001</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="6" t="n">
         <v>45367</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -2343,7 +1798,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2353,7 +1808,7 @@
           <t>INV-2024-00014</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="6" t="n">
         <v>45446</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -2366,7 +1821,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2376,7 +1831,7 @@
           <t>INV-2024-00017</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="6" t="n">
         <v>45452</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -2389,7 +1844,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Cutoff</t>
         </is>
       </c>
     </row>
@@ -2399,7 +1854,7 @@
           <t>INV-2024-00009</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>45406</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -2412,7 +1867,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2422,7 +1877,7 @@
           <t>INV-2024-00041</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>45308</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2445,7 +1900,7 @@
           <t>INV-2024-00026</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="6" t="n">
         <v>45354</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -2468,7 +1923,7 @@
           <t>INV-2024-00030</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="6" t="n">
         <v>45372</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2481,7 +1936,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2491,7 +1946,7 @@
           <t>INV-2024-00022</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="6" t="n">
         <v>45454</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2514,7 +1969,7 @@
           <t>INV-2024-00031</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="6" t="n">
         <v>45346</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2527,7 +1982,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2537,7 +1992,7 @@
           <t>INV-2024-00005</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="6" t="n">
         <v>45300</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2560,7 +2015,7 @@
           <t>INV-2024-00029</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="6" t="n">
         <v>45306</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -2573,7 +2028,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2038,7 @@
           <t>INV-2024-00018</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="6" t="n">
         <v>45384</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2606,7 +2061,7 @@
           <t>INV-2024-00025</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="6" t="n">
         <v>45447</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2629,7 +2084,7 @@
           <t>INV-2024-00003</t>
         </is>
       </c>
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="6" t="n">
         <v>45318</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2642,7 +2097,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2107,7 @@
           <t>INV-2024-00027</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="6" t="n">
         <v>45361</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -2665,7 +2120,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2130,7 @@
           <t>INV-2024-00045</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="6" t="n">
         <v>45360</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2688,7 +2143,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2153,7 @@
           <t>INV-2024-00038</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="6" t="n">
         <v>45327</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -2721,7 +2176,7 @@
           <t>INV-2024-00033</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>45393</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2734,7 +2189,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2199,7 @@
           <t>INV-2024-00006</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="6" t="n">
         <v>45351</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -2757,7 +2212,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2222,7 @@
           <t>INV-2024-00036</t>
         </is>
       </c>
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="6" t="n">
         <v>45441</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2780,7 +2235,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2245,7 @@
           <t>INV-2024-00004</t>
         </is>
       </c>
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>45431</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -2803,7 +2258,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2268,7 @@
           <t>INV-2024-00016</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="6" t="n">
         <v>45388</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2826,7 +2281,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2291,7 @@
           <t>INV-2024-00020</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="6" t="n">
         <v>45366</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -2849,7 +2304,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2314,7 @@
           <t>INV-2024-LARGE-003</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="6" t="n">
         <v>45359</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2872,7 +2327,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2337,7 @@
           <t>INV-2024-00008</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="6" t="n">
         <v>45471</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2905,7 +2360,7 @@
           <t>INV-2024-00002</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="6" t="n">
         <v>45362</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2918,7 +2373,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2383,7 @@
           <t>INV-2024-00032</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="6" t="n">
         <v>45372</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -2941,7 +2396,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2406,7 @@
           <t>INV-2024-00021</t>
         </is>
       </c>
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="6" t="n">
         <v>45317</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2974,7 +2429,7 @@
           <t>INV-2024-00039</t>
         </is>
       </c>
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="6" t="n">
         <v>45304</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -2997,7 +2452,7 @@
           <t>INV-2024-00001</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>45455</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3020,7 +2475,7 @@
           <t>INV-2024-00034</t>
         </is>
       </c>
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="6" t="n">
         <v>45359</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -3043,7 +2498,7 @@
           <t>INV-2024-00035</t>
         </is>
       </c>
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="6" t="n">
         <v>45435</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3056,7 +2511,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
@@ -3066,7 +2521,7 @@
           <t>INV-2024-00011</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="6" t="n">
         <v>45379</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -3089,7 +2544,7 @@
           <t>INV-2024-00024</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="6" t="n">
         <v>45471</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3102,7 +2557,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Cutoff</t>
         </is>
       </c>
     </row>
@@ -3112,7 +2567,7 @@
           <t>INV-2024-00010</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="6" t="n">
         <v>45293</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -3125,7 +2580,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
@@ -3135,7 +2590,7 @@
           <t>INV-2024-00013</t>
         </is>
       </c>
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="6" t="n">
         <v>45316</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3148,7 +2603,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>

--- a/outputs/Revenue_Test_Workpaper.xlsx
+++ b/outputs/Revenue_Test_Workpaper.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="5">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -668,7 +668,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>28773caf-8d05-4f09-baab-b41c0733e4bb</t>
+          <t>57d6d640-0745-4a71-822f-0f0bd8faf952</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>46140.88422349308</v>
+        <v>46146.82478828209</v>
       </c>
     </row>
     <row r="19">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>10268454.35</v>
+        <v>30704253.77</v>
       </c>
     </row>
     <row r="21">
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9976071.85</v>
+        <v>30140795.34</v>
       </c>
     </row>
     <row r="22">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>292382.5</v>
+        <v>563458.4300000001</v>
       </c>
     </row>
     <row r="23">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
     </row>
   </sheetData>
@@ -743,12 +743,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>45355</v>
+        <v>45292</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>100813.52</v>
+        <v>341692.95</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>45324</v>
+        <v>45292</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>191014.76</v>
+        <v>300039.02</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45384</v>
+        <v>45295</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>815882</v>
+        <v>195180.16</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -870,17 +870,19 @@
           <t>INV-2024-004</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="6" t="n">
+        <v>45296</v>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>171751.61</v>
+        <v>299781.08</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -894,17 +896,19 @@
           <t>INV-2024-005</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>45298</v>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76263.60000000001</v>
+        <v>236442.89</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -918,17 +922,19 @@
           <t>INV-2024-006</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>45300</v>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>180042.41</v>
+        <v>129109.72</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -942,17 +948,19 @@
           <t>INV-2024-007</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="6" t="n">
+        <v>45300</v>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Digital Innovations Co</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>580873.8199999999</v>
+        <v>977177.14</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -963,22 +971,22 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-009</t>
+          <t>INV-2024-008</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45353</v>
+        <v>45306</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>178846.37</v>
+        <v>278643.74</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -989,22 +997,22 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-010</t>
+          <t>INV-2024-009</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45295</v>
+        <v>45304</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>79004.13</v>
+        <v>471477.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1015,20 +1023,22 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-011</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
+          <t>INV-2024-012</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>45310</v>
+      </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>163863.75</v>
+        <v>442917.91</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1039,20 +1049,22 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-012</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
+          <t>INV-2024-013</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>45311</v>
+      </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Meridian Health Group</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1222029.35</v>
+        <v>376571.26</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1063,20 +1075,22 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-015</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+          <t>INV-2024-014</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>45313</v>
+      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>71514.46000000001</v>
+        <v>1814656.71</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1087,20 +1101,22 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-016</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
+          <t>INV-2024-015</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>45316</v>
+      </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>151663.55</v>
+        <v>385351.18</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1111,20 +1127,22 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-018</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
+          <t>INV-2024-016</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>45318</v>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>ABC Technology Pty Ltd</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>845362.55</v>
+        <v>173086.94</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1135,22 +1153,22 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-019</t>
+          <t>INV-2024-017</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>45475</v>
+        <v>45323</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>52178.13</v>
+        <v>149961.43</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1161,22 +1179,22 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-020</t>
+          <t>INV-2024-018</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>45386</v>
+        <v>45325</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>163001.07</v>
+        <v>82905.42999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1187,22 +1205,22 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-022</t>
+          <t>INV-2024-020</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>45352</v>
+        <v>45328</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>154272.88</v>
+        <v>362309.25</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1213,22 +1231,22 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-024</t>
+          <t>INV-2024-021</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>45355</v>
+        <v>45327</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>111750.79</v>
+        <v>682346.4</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1239,20 +1257,22 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-025</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
+          <t>INV-2024-023</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>45333</v>
+      </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>912967.3100000001</v>
+        <v>486071.82</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1263,20 +1283,22 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-026</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
+          <t>INV-2024-024</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>45333</v>
+      </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>138775.96</v>
+        <v>382063.08</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1287,20 +1309,22 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-027</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n"/>
+          <t>INV-2024-025</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>45336</v>
+      </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>164864.62</v>
+        <v>256078.65</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1311,20 +1335,22 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-028</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
+          <t>INV-2024-027</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>45339</v>
+      </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>51078.42</v>
+        <v>314353.27</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1335,22 +1361,22 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-029</t>
+          <t>INV-2024-028</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45539</v>
+        <v>45339</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Meridian Health Group</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>183237.59</v>
+        <v>1150543.61</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -1361,22 +1387,22 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-030</t>
+          <t>INV-2024-029</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>45508</v>
+        <v>45342</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>116860.72</v>
+        <v>421554.35</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1387,20 +1413,22 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-031</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
+          <t>INV-2024-030</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>45346</v>
+      </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>71760.28999999999</v>
+        <v>256069.34</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1411,22 +1439,22 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-033</t>
+          <t>INV-2024-031</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>45505</v>
+        <v>45346</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>ABC Technology Pty Ltd</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>50785.35</v>
+        <v>103096.86</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -1437,20 +1465,22 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-034</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
+          <t>INV-2024-032</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>45348</v>
+      </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>178198.51</v>
+        <v>189802.77</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -1461,22 +1491,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-036</t>
+          <t>INV-2024-033</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>45388</v>
+        <v>45349</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>115169.24</v>
+        <v>84585.64999999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1487,20 +1517,22 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-037</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n"/>
+          <t>INV-2024-035</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>45354</v>
+      </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>100747.14</v>
+        <v>1496258.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1511,22 +1543,22 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-038</t>
+          <t>INV-2024-036</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>45415</v>
+        <v>45353</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>127303.87</v>
+        <v>461569.6</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -1537,22 +1569,22 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-040</t>
+          <t>INV-2024-037</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>45292</v>
+        <v>45355</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Digital Innovations Co</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>175071.93</v>
+        <v>459617.23</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -1563,20 +1595,22 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-041</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
+          <t>INV-2024-038</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>45360</v>
+      </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>135008.67</v>
+        <v>301295.26</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -1587,20 +1621,22 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-042</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
+          <t>INV-2024-039</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>45359</v>
+      </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>168085.43</v>
+        <v>246627.37</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -1611,20 +1647,22 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-043</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
+          <t>INV-2024-041</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>45468</v>
+      </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>173971.81</v>
+        <v>184385.92</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -1635,20 +1673,22 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-044</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n"/>
+          <t>INV-2024-042</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>45469</v>
+      </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>196867.74</v>
+        <v>1635090.2</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -1659,22 +1699,22 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-046</t>
+          <t>INV-2024-043</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>45509</v>
+        <v>45469</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Meridian Health Group</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>136111.8</v>
+        <v>492727.4</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -1685,20 +1725,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-047</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n"/>
+          <t>INV-2024-044</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>45471</v>
+      </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>106009.87</v>
+        <v>404265.69</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -1709,20 +1751,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-048</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n"/>
+          <t>INV-2024-045</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>45468</v>
+      </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>114484.02</v>
+        <v>123183.19</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -1733,22 +1777,22 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-049</t>
+          <t>INV-2024-047</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>45296</v>
+        <v>45470</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>74173.35000000001</v>
+        <v>285645.03</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -1759,20 +1803,22 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-050</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="n"/>
+          <t>INV-2024-049</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>45470</v>
+      </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>67965.07000000001</v>
+        <v>701472.65</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -1783,20 +1829,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-051</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
+          <t>INV-2024-050</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>45383</v>
+      </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>150057.76</v>
+        <v>367172.39</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -1807,22 +1855,22 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-052</t>
+          <t>INV-2024-051</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>45416</v>
+        <v>45383</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>107528.89</v>
+        <v>408847.87</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -1833,20 +1881,22 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-053</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
+          <t>INV-2024-052</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>45387</v>
+      </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>Digital Innovations Co</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>59009.36</v>
+        <v>489092.31</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -1857,22 +1907,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-054</t>
+          <t>INV-2024-053</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>45444</v>
+        <v>45387</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>139176.5</v>
+        <v>268477.15</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -1886,17 +1936,19 @@
           <t>INV-2024-055</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n"/>
+      <c r="B46" s="6" t="n">
+        <v>45389</v>
+      </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>160906.07</v>
+        <v>331421.99</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -1910,17 +1962,19 @@
           <t>INV-2024-056</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
+      <c r="B47" s="6" t="n">
+        <v>45390</v>
+      </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>164609.93</v>
+        <v>710885.37</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -1934,17 +1988,19 @@
           <t>INV-2024-057</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
+      <c r="B48" s="6" t="n">
+        <v>45392</v>
+      </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>187086.65</v>
+        <v>473665.93</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -1955,20 +2011,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-058</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
+          <t>INV-2024-059</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>45398</v>
+      </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>66431.92999999999</v>
+        <v>265983.83</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -1982,55 +2040,785 @@
           <t>INV-2024-060</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
+      <c r="B50" s="6" t="n">
+        <v>45397</v>
+      </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
+          <t>Harbour Consulting Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>305085.16</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-061</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>45400</v>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>ABC Technology Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>482343.43</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-062</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>45401</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>XYZ Services Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>464779.85</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-063</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>45406</v>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Global Manufacturing Co</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>378745.02</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-064</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>45407</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Health Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>346343.5</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-065</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>45410</v>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Fintech Partners Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>357779.25</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-066</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>45410</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Metro Construction Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>202228</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-067</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>45411</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Digital Innovations Co</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>337335.81</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-068</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>45414</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Retail Group</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>189558.34</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-069</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>45416</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Northern Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>450263.34</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-071</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>45419</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Coastal Engineering Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>127371.42</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-074</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>45424</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Summit Legal Services</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>278988.38</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-075</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>45429</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Harbour Consulting Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>296090.78</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-077</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>45429</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>XYZ Services Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>355248.46</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-081</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>45440</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Metro Construction Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>168257.75</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-083</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>45441</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Retail Group</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>142518.28</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-084</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>45441</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Northern Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>245046.27</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-085</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>45444</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
           <t>Community Services NFP</t>
         </is>
       </c>
-      <c r="D50" s="4" t="n">
-        <v>71637.3</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>Amount exceeds threshold</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="3" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="3" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="D67" s="4" t="n">
+        <v>271711.35</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-086</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>45445</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Coastal Engineering Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>362933.76</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-087</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>45449</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Alpine Software Co</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>441726.15</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-088</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>45452</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Meridian Health Group</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>290032.13</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-089</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>45452</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Summit Legal Services</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>124939.54</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-090</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>45452</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Harbour Consulting Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>238882.05</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-091</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>45455</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>ABC Technology Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>206225.15</v>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-093</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>45460</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Global Manufacturing Co</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>331041.45</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-095</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>45464</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Fintech Partners Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>208227.95</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-096</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>45466</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Metro Construction Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>432537.29</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-098</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>45468</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Retail Group</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>328302.94</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-099</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>45471</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Northern Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>324698.15</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Amount exceeds threshold</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="3" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B80" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C52" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="C80" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
         <is>
           <t>Total value</t>
         </is>
       </c>
-      <c r="E52" s="10" t="n">
-        <v>9976071.85</v>
-      </c>
-      <c r="F52" s="3" t="n"/>
+      <c r="E80" s="10" t="n">
+        <v>30140795.34</v>
+      </c>
+      <c r="F80" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
@@ -2044,16 +2832,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -2112,21 +2900,23 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-014</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="n"/>
+          <t>INV-2024-026</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>45339</v>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>16756.2</v>
+        <v>57267.18</v>
       </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n">
-        <v>73095.625</v>
+        <v>112691.686</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -2140,23 +2930,23 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-021</t>
+          <t>INV-2024-048</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>45505</v>
+        <v>45469</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>34128.99</v>
+        <v>43565.99</v>
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n">
-        <v>73095.625</v>
+        <v>112691.686</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -2170,23 +2960,23 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-035</t>
+          <t>INV-2024-072</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>45417</v>
+        <v>45419</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>30825.27</v>
+        <v>36267.37</v>
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n">
-        <v>73095.625</v>
+        <v>112691.686</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -2200,21 +2990,23 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-059</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
+          <t>INV-2024-079</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>45435</v>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>30445.37</v>
+        <v>37939.25</v>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n">
-        <v>73095.625</v>
+        <v>112691.686</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -2223,40 +3015,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="4" t="n"/>
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-100</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>45472</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Community Services NFP</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>34576.28</v>
+      </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="3" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>112691.686</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Residual population MUS: cumulative value crossed sampling interval point</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Sample size</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Total value</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>112155.83</v>
-      </c>
+      <c r="A8" s="3" t="n"/>
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Sample size</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Total value</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>209616.07</v>
+      </c>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>
@@ -2273,12 +3095,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -2328,19 +3150,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INV-2024-054</t>
+          <t>INV-2024-100</t>
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>45444</v>
+        <v>45472</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D3" s="13" t="n">
-        <v>139176.5</v>
+        <v>34576.28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2351,19 +3173,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INV-2024-035</t>
+          <t>INV-2024-040</t>
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>45417</v>
+        <v>45472</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D4" s="13" t="n">
-        <v>30825.27</v>
+        <v>59970.83</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2374,19 +3196,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INV-2024-052</t>
+          <t>INV-2024-099</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>45416</v>
+        <v>45471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D5" s="13" t="n">
-        <v>107528.89</v>
+        <v>324698.15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2397,19 +3219,19 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INV-2024-038</t>
+          <t>INV-2024-044</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>45415</v>
+        <v>45471</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>127303.87</v>
+        <v>404265.69</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2420,19 +3242,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INV-2024-036</t>
+          <t>INV-2024-047</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>45388</v>
+        <v>45470</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>115169.24</v>
+        <v>285645.03</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2482,121 +3304,6 @@
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Days from Cutoff</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INV-2024-008</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>45475</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pacific Retail Group</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>5479.86</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INV-2024-019</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>45475</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Northern Biotech Ltd</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>52178.13</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>INV-2024-021</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>45505</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ABC Technology Pty Ltd</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>34128.99</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>INV-2024-033</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>45505</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Global Manufacturing Co</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>50785.35</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INV-2024-030</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>45508</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Community Services NFP</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>116860.72</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>post</t>
         </is>
       </c>
     </row>
@@ -2615,12 +3322,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
@@ -2659,7 +3366,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>45355</v>
+        <v>45292</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
@@ -2667,7 +3374,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>100813.52</v>
+        <v>341692.95</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -2682,7 +3389,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>45324</v>
+        <v>45292</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -2690,7 +3397,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>191014.76</v>
+        <v>300039.02</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -2705,7 +3412,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45384</v>
+        <v>45295</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -2713,7 +3420,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>815882</v>
+        <v>195180.16</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -2727,14 +3434,16 @@
           <t>INV-2024-004</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
+      <c r="B5" s="6" t="n">
+        <v>45296</v>
+      </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>171751.61</v>
+        <v>299781.08</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -2748,14 +3457,16 @@
           <t>INV-2024-005</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="B6" s="6" t="n">
+        <v>45298</v>
+      </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76263.60000000001</v>
+        <v>236442.89</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -2769,14 +3480,16 @@
           <t>INV-2024-006</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>45300</v>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>180042.41</v>
+        <v>129109.72</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -2790,14 +3503,16 @@
           <t>INV-2024-007</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
+      <c r="B8" s="6" t="n">
+        <v>45300</v>
+      </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Digital Innovations Co</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>580873.8199999999</v>
+        <v>977177.14</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -2812,7 +3527,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>45475</v>
+        <v>45306</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -2820,11 +3535,11 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5479.86</v>
+        <v>278643.74</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
@@ -2835,7 +3550,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45353</v>
+        <v>45304</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -2843,7 +3558,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>178846.37</v>
+        <v>471477.1</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -2854,40 +3569,42 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-010</t>
+          <t>INV-2024-011</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>45295</v>
+        <v>45311</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>79004.13</v>
+        <v>61300.64</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-011</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
+          <t>INV-2024-012</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>45310</v>
+      </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>163863.75</v>
+        <v>442917.91</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -2898,17 +3615,19 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-012</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+          <t>INV-2024-013</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>45311</v>
+      </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Meridian Health Group</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1222029.35</v>
+        <v>376571.26</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -2919,61 +3638,65 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-013</t>
+          <t>INV-2024-014</t>
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45387</v>
+        <v>45313</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>46538.13</v>
+        <v>1814656.71</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Not Selected</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-014</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
+          <t>INV-2024-015</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>45316</v>
+      </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>16756.2</v>
+        <v>385351.18</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-015</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
+          <t>INV-2024-016</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>45318</v>
+      </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>ABC Technology Pty Ltd</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>71514.46000000001</v>
+        <v>173086.94</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -2984,17 +3707,19 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-016</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
+          <t>INV-2024-017</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>45323</v>
+      </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>151663.55</v>
+        <v>149961.43</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -3005,86 +3730,88 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-017</t>
+          <t>INV-2024-018</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>45296</v>
+        <v>45325</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>35206.57</v>
+        <v>82905.42999999999</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Not Selected</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-018</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
+          <t>INV-2024-019</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>45322</v>
+      </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>845362.55</v>
+        <v>6153.36</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-019</t>
+          <t>INV-2024-020</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>45475</v>
+        <v>45328</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>52178.13</v>
+        <v>362309.25</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-020</t>
+          <t>INV-2024-021</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>45386</v>
+        <v>45327</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>163001.07</v>
+        <v>682346.4</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -3095,42 +3822,42 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-021</t>
+          <t>INV-2024-023</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45505</v>
+        <v>45333</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>34128.99</v>
+        <v>486071.82</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>MUS/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-022</t>
+          <t>INV-2024-024</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45352</v>
+        <v>45333</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>154272.88</v>
+        <v>382063.08</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -3141,63 +3868,65 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-023</t>
+          <t>INV-2024-025</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>45538</v>
+        <v>45336</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>40118.92</v>
+        <v>256078.65</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Not Selected</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-024</t>
+          <t>INV-2024-026</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>45355</v>
+        <v>45339</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>111750.79</v>
+        <v>57267.18</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-025</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
+          <t>INV-2024-027</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>45339</v>
+      </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>912967.3100000001</v>
+        <v>314353.27</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -3208,17 +3937,19 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-026</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
+          <t>INV-2024-028</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>45339</v>
+      </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Meridian Health Group</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>138775.96</v>
+        <v>1150543.61</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -3229,17 +3960,19 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-027</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
+          <t>INV-2024-029</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>45342</v>
+      </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>164864.62</v>
+        <v>421554.35</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -3250,17 +3983,19 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-028</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
+          <t>INV-2024-030</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>45346</v>
+      </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>51078.42</v>
+        <v>256069.34</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -3271,19 +4006,19 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-029</t>
+          <t>INV-2024-031</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>45539</v>
+        <v>45346</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>ABC Technology Pty Ltd</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>183237.59</v>
+        <v>103096.86</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -3294,40 +4029,42 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-030</t>
+          <t>INV-2024-032</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>45508</v>
+        <v>45348</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>116860.72</v>
+        <v>189802.77</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-031</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
+          <t>INV-2024-033</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>45349</v>
+      </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>71760.28999999999</v>
+        <v>84585.64999999999</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -3338,63 +4075,65 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-032</t>
+          <t>INV-2024-035</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>45353</v>
+        <v>45354</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>16976.62</v>
+        <v>1496258.3</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Not Selected</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-033</t>
+          <t>INV-2024-036</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>45505</v>
+        <v>45353</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>50785.35</v>
+        <v>461569.6</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-034</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
+          <t>INV-2024-037</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>45355</v>
+      </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Digital Innovations Co</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>178198.51</v>
+        <v>459617.23</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -3405,130 +4144,134 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-035</t>
+          <t>INV-2024-038</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>45417</v>
+        <v>45360</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>30825.27</v>
+        <v>301295.26</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>MUS/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-036</t>
+          <t>INV-2024-039</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>45388</v>
+        <v>45359</v>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>115169.24</v>
+        <v>246627.37</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-037</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n"/>
+          <t>INV-2024-040</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>45472</v>
+      </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>100747.14</v>
+        <v>59970.83</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Cutoff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-038</t>
+          <t>INV-2024-041</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>45415</v>
+        <v>45468</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>127303.87</v>
+        <v>184385.92</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-039</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n"/>
+          <t>INV-2024-042</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>45469</v>
+      </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>25175.28</v>
+        <v>1635090.2</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Not Selected</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-040</t>
+          <t>INV-2024-043</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>45292</v>
+        <v>45469</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Meridian Health Group</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>175071.93</v>
+        <v>492727.4</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -3539,38 +4282,42 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-041</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n"/>
+          <t>INV-2024-044</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>45471</v>
+      </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>135008.67</v>
+        <v>404265.69</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Target/Cutoff</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-042</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n"/>
+          <t>INV-2024-045</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>45468</v>
+      </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>168085.43</v>
+        <v>123183.19</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -3581,84 +4328,88 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-043</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n"/>
+          <t>INV-2024-047</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>45470</v>
+      </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>173971.81</v>
+        <v>285645.03</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Target/Cutoff</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-044</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n"/>
+          <t>INV-2024-048</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>45469</v>
+      </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>196867.74</v>
+        <v>43565.99</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>MUS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-045</t>
+          <t>INV-2024-049</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>45630</v>
+        <v>45470</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>10731.29</v>
+        <v>701472.65</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Not Selected</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-046</t>
+          <t>INV-2024-050</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>45509</v>
+        <v>45383</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>Fintech Partners Pty Ltd</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>136111.8</v>
+        <v>367172.39</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -3669,17 +4420,19 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-047</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n"/>
+          <t>INV-2024-051</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>45383</v>
+      </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>Metro Construction Pty Ltd</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>106009.87</v>
+        <v>408847.87</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -3690,17 +4443,19 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-048</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
+          <t>INV-2024-052</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>45387</v>
+      </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Digital Innovations Co</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>114484.02</v>
+        <v>489092.31</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -3711,19 +4466,19 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-049</t>
+          <t>INV-2024-053</t>
         </is>
       </c>
       <c r="B50" s="6" t="n">
-        <v>45296</v>
+        <v>45387</v>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Pacific Retail Group</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>74173.35000000001</v>
+        <v>268477.15</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -3734,38 +4489,42 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-050</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n"/>
+          <t>INV-2024-054</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>45390</v>
+      </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Community Services NFP</t>
+          <t>Northern Biotech Ltd</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>67965.07000000001</v>
+        <v>66854.07000000001</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Not Selected</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-051</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n"/>
+          <t>INV-2024-055</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>45389</v>
+      </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ABC Technology Pty Ltd</t>
+          <t>Community Services NFP</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>150057.76</v>
+        <v>331421.99</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -3776,40 +4535,42 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-052</t>
+          <t>INV-2024-056</t>
         </is>
       </c>
       <c r="B53" s="6" t="n">
-        <v>45416</v>
+        <v>45390</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>XYZ Services Pty Ltd</t>
+          <t>Coastal Engineering Pty Ltd</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>107528.89</v>
+        <v>710885.37</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-053</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="n"/>
+          <t>INV-2024-057</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>45392</v>
+      </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Global Manufacturing Co</t>
+          <t>Alpine Software Co</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>59009.36</v>
+        <v>473665.93</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -3820,40 +4581,42 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-054</t>
+          <t>INV-2024-059</t>
         </is>
       </c>
       <c r="B55" s="6" t="n">
-        <v>45444</v>
+        <v>45398</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Health Solutions Ltd</t>
+          <t>Summit Legal Services</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>139176.5</v>
+        <v>265983.83</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Target/Cutoff</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-055</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n"/>
+          <t>INV-2024-060</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>45397</v>
+      </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Fintech Partners Pty Ltd</t>
+          <t>Harbour Consulting Pty Ltd</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>160906.07</v>
+        <v>305085.16</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -3864,17 +4627,19 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-056</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="n"/>
+          <t>INV-2024-061</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>45400</v>
+      </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Metro Construction Pty Ltd</t>
+          <t>ABC Technology Pty Ltd</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>164609.93</v>
+        <v>482343.43</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -3885,17 +4650,19 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-057</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n"/>
+          <t>INV-2024-062</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>45401</v>
+      </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Digital Innovations Co</t>
+          <t>XYZ Services Pty Ltd</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>187086.65</v>
+        <v>464779.85</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -3906,17 +4673,19 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-058</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n"/>
+          <t>INV-2024-063</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>45406</v>
+      </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Pacific Retail Group</t>
+          <t>Global Manufacturing Co</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>66431.92999999999</v>
+        <v>378745.02</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -3927,42 +4696,782 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-059</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n"/>
+          <t>INV-2024-064</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>45407</v>
+      </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Northern Biotech Ltd</t>
+          <t>Health Solutions Ltd</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>30445.37</v>
+        <v>346343.5</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>Target</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>INV-2024-060</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="n"/>
+          <t>INV-2024-065</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>45410</v>
+      </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
+          <t>Fintech Partners Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>357779.25</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-066</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>45410</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Metro Construction Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>202228</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-067</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>45411</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Digital Innovations Co</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>337335.81</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-068</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>45414</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Retail Group</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>189558.34</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-069</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>45416</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Northern Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>450263.34</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-071</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>45419</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Coastal Engineering Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>127371.42</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-072</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>45419</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Alpine Software Co</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>36267.37</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-073</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>45425</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Meridian Health Group</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>14966.97</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Not Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-074</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>45424</v>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Summit Legal Services</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>278988.38</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-075</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>45429</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Harbour Consulting Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>296090.78</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-076</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>45428</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>ABC Technology Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>8108.19</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Not Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-077</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>45429</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>XYZ Services Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>355248.46</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-078</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>45433</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Global Manufacturing Co</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="n">
+        <v>33714.73</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Not Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-079</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>45435</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Health Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>37939.25</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>MUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-080</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>45436</v>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Fintech Partners Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>20109.15</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Not Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-081</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>45440</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Metro Construction Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>168257.75</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-083</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>45441</v>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Retail Group</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>142518.28</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-084</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>45441</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Northern Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>245046.27</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-085</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>45444</v>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
           <t>Community Services NFP</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>71637.3</v>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>Target</t>
+      <c r="D79" s="4" t="n">
+        <v>271711.35</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-086</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>45445</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Coastal Engineering Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>362933.76</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-087</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>45449</v>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Alpine Software Co</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>441726.15</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-088</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>45452</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Meridian Health Group</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>290032.13</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-089</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>45452</v>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Summit Legal Services</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>124939.54</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-090</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>45452</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Harbour Consulting Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>238882.05</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-091</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>45455</v>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>ABC Technology Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>206225.15</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-092</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>45460</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>XYZ Services Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>51279.6</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Not Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-093</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>45460</v>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Global Manufacturing Co</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>331041.45</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-095</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>45464</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Fintech Partners Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>208227.95</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-096</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n">
+        <v>45466</v>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Metro Construction Pty Ltd</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>432537.29</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-097</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>45468</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Digital Innovations Co</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>31384.82</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Not Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-098</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>45468</v>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Retail Group</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>328302.94</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-099</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>45471</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Northern Biotech Ltd</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>324698.15</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Target/Cutoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>INV-2024-100</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>45472</v>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Community Services NFP</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>34576.28</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>MUS/Cutoff</t>
         </is>
       </c>
     </row>
